--- a/software/python_processing/dataset_stats/cLASIr Dataset Multi Stats.xlsx
+++ b/software/python_processing/dataset_stats/cLASIr Dataset Multi Stats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,17 +436,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Class 0.0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Class 1.0</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Class 2.0</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Class 0.0</t>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Class 4.0</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Class 3.0</t>
         </is>
       </c>
     </row>
@@ -457,12 +467,18 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>416</v>
+      </c>
+      <c r="C2" t="n">
         <v>972</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>214</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>754</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -471,10 +487,16 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>212</v>
+      </c>
+      <c r="C3" t="n">
         <v>1138</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>1036</v>
+      </c>
+      <c r="F3" t="n">
         <v>322</v>
       </c>
     </row>
@@ -485,12 +507,18 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>450</v>
+      </c>
+      <c r="C4" t="n">
         <v>904</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>236</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>736</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -499,10 +527,16 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>294</v>
+      </c>
+      <c r="C5" t="n">
         <v>890</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>740</v>
+      </c>
+      <c r="F5" t="n">
         <v>228</v>
       </c>
     </row>
@@ -513,12 +547,18 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>748</v>
+      </c>
+      <c r="C6" t="n">
         <v>998</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>200</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>772</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -527,10 +567,16 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="n">
         <v>904</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>547</v>
+      </c>
+      <c r="F7" t="n">
         <v>180</v>
       </c>
     </row>
@@ -541,12 +587,18 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>404</v>
+      </c>
+      <c r="C8" t="n">
         <v>1298</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>234</v>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>818</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -555,10 +607,16 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>294</v>
+      </c>
+      <c r="C9" t="n">
         <v>960</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>744</v>
+      </c>
+      <c r="F9" t="n">
         <v>294</v>
       </c>
     </row>
@@ -569,12 +627,18 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>314</v>
+      </c>
+      <c r="C10" t="n">
         <v>972</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>264</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>734</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -583,10 +647,16 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>272</v>
+      </c>
+      <c r="C11" t="n">
         <v>954</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>882</v>
+      </c>
+      <c r="F11" t="n">
         <v>384</v>
       </c>
     </row>
@@ -597,12 +667,18 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>438</v>
+      </c>
+      <c r="C12" t="n">
         <v>1008</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>262</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>786</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -611,10 +687,16 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>297</v>
+      </c>
+      <c r="C13" t="n">
         <v>886</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>712</v>
+      </c>
+      <c r="F13" t="n">
         <v>230</v>
       </c>
     </row>
@@ -625,12 +707,18 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>386</v>
+      </c>
+      <c r="C14" t="n">
         <v>950</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>222</v>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>934</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -639,10 +727,16 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>343</v>
+      </c>
+      <c r="C15" t="n">
         <v>976</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>894</v>
+      </c>
+      <c r="F15" t="n">
         <v>242</v>
       </c>
     </row>
@@ -653,12 +747,18 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>370</v>
+      </c>
+      <c r="C16" t="n">
         <v>859</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>290</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>739</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -667,10 +767,16 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>330</v>
+      </c>
+      <c r="C17" t="n">
         <v>920</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="n">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>730</v>
+      </c>
+      <c r="F17" t="n">
         <v>226</v>
       </c>
     </row>
@@ -681,12 +787,18 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>472</v>
+      </c>
+      <c r="C18" t="n">
         <v>926</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>232</v>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>766</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -695,10 +807,16 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>284</v>
+      </c>
+      <c r="C19" t="n">
         <v>1026</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>812</v>
+      </c>
+      <c r="F19" t="n">
         <v>214</v>
       </c>
     </row>
@@ -709,12 +827,18 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>352</v>
+      </c>
+      <c r="C20" t="n">
         <v>938</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>246</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>738</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -723,10 +847,16 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>420</v>
+      </c>
+      <c r="C21" t="n">
         <v>886</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="n">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>660</v>
+      </c>
+      <c r="F21" t="n">
         <v>224</v>
       </c>
     </row>
@@ -737,12 +867,18 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>324</v>
+      </c>
+      <c r="C22" t="n">
         <v>856</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>254</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>726</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -751,10 +887,16 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>292</v>
+      </c>
+      <c r="C23" t="n">
         <v>952</v>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="n">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>818</v>
+      </c>
+      <c r="F23" t="n">
         <v>212</v>
       </c>
     </row>
@@ -765,10 +907,16 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>358</v>
+      </c>
+      <c r="C24" t="n">
         <v>950</v>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>744</v>
+      </c>
+      <c r="F24" t="n">
         <v>208</v>
       </c>
     </row>
@@ -779,10 +927,16 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>286</v>
+      </c>
+      <c r="C25" t="n">
         <v>902</v>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="n">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>794</v>
+      </c>
+      <c r="F25" t="n">
         <v>232</v>
       </c>
     </row>
@@ -793,10 +947,16 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>275</v>
+      </c>
+      <c r="C26" t="n">
         <v>916</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="n">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>804</v>
+      </c>
+      <c r="F26" t="n">
         <v>232</v>
       </c>
     </row>
@@ -807,12 +967,18 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>427</v>
+      </c>
+      <c r="C27" t="n">
         <v>956</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>246</v>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>702</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -821,10 +987,16 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>279</v>
+      </c>
+      <c r="C28" t="n">
         <v>914</v>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>730</v>
+      </c>
+      <c r="F28" t="n">
         <v>216</v>
       </c>
     </row>
@@ -835,12 +1007,18 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>446</v>
+      </c>
+      <c r="C29" t="n">
         <v>876</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>266</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>656</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -849,10 +1027,16 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>337</v>
+      </c>
+      <c r="C30" t="n">
         <v>1088</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="n">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>852</v>
+      </c>
+      <c r="F30" t="n">
         <v>228</v>
       </c>
     </row>
@@ -863,12 +1047,18 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>442</v>
+      </c>
+      <c r="C31" t="n">
         <v>916</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>246</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>782</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -877,10 +1067,16 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>346</v>
+      </c>
+      <c r="C32" t="n">
         <v>962</v>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="n">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>794</v>
+      </c>
+      <c r="F32" t="n">
         <v>242</v>
       </c>
     </row>
@@ -891,12 +1087,18 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>318</v>
+      </c>
+      <c r="C33" t="n">
         <v>1094</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>230</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>866</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -905,10 +1107,16 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>291</v>
+      </c>
+      <c r="C34" t="n">
         <v>936</v>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="n">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>746</v>
+      </c>
+      <c r="F34" t="n">
         <v>254</v>
       </c>
     </row>
@@ -919,12 +1127,18 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>344</v>
+      </c>
+      <c r="C35" t="n">
         <v>868</v>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>246</v>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>666</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -933,10 +1147,16 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>372</v>
+      </c>
+      <c r="C36" t="n">
         <v>1016</v>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="n">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>806</v>
+      </c>
+      <c r="F36" t="n">
         <v>230</v>
       </c>
     </row>
@@ -947,12 +1167,18 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>464</v>
+      </c>
+      <c r="C37" t="n">
         <v>1144</v>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>254</v>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>760</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -961,10 +1187,16 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>380</v>
+      </c>
+      <c r="C38" t="n">
         <v>862</v>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="n">
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>704</v>
+      </c>
+      <c r="F38" t="n">
         <v>242</v>
       </c>
     </row>
@@ -975,12 +1207,18 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>302</v>
+      </c>
+      <c r="C39" t="n">
         <v>950</v>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>260</v>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>746</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -989,10 +1227,16 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>258</v>
+      </c>
+      <c r="C40" t="n">
         <v>928</v>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="n">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>718</v>
+      </c>
+      <c r="F40" t="n">
         <v>234</v>
       </c>
     </row>
@@ -1003,12 +1247,18 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>474</v>
+      </c>
+      <c r="C41" t="n">
         <v>1016</v>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>230</v>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>748</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -1017,10 +1267,16 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>320</v>
+      </c>
+      <c r="C42" t="n">
         <v>1090</v>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="n">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>792</v>
+      </c>
+      <c r="F42" t="n">
         <v>210</v>
       </c>
     </row>
@@ -1031,12 +1287,18 @@
         </is>
       </c>
       <c r="B43" t="n">
+        <v>396</v>
+      </c>
+      <c r="C43" t="n">
         <v>1044</v>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>234</v>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>800</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1045,10 +1307,16 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>298</v>
+      </c>
+      <c r="C44" t="n">
         <v>1004</v>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="n">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>796</v>
+      </c>
+      <c r="F44" t="n">
         <v>220</v>
       </c>
     </row>
@@ -1059,12 +1327,18 @@
         </is>
       </c>
       <c r="B45" t="n">
+        <v>521</v>
+      </c>
+      <c r="C45" t="n">
         <v>910</v>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>224</v>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>754</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1073,10 +1347,16 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>362</v>
+      </c>
+      <c r="C46" t="n">
         <v>1034</v>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="n">
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>786</v>
+      </c>
+      <c r="F46" t="n">
         <v>232</v>
       </c>
     </row>
@@ -1087,12 +1367,18 @@
         </is>
       </c>
       <c r="B47" t="n">
+        <v>492</v>
+      </c>
+      <c r="C47" t="n">
         <v>950</v>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>239</v>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>765</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1101,12 +1387,18 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>435</v>
+      </c>
+      <c r="C48" t="n">
         <v>952</v>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>226</v>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>692</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -1115,10 +1407,16 @@
         </is>
       </c>
       <c r="B49" t="n">
+        <v>36</v>
+      </c>
+      <c r="C49" t="n">
         <v>1078</v>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="n">
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>858</v>
+      </c>
+      <c r="F49" t="n">
         <v>224</v>
       </c>
     </row>
@@ -1129,12 +1427,18 @@
         </is>
       </c>
       <c r="B50" t="n">
+        <v>504</v>
+      </c>
+      <c r="C50" t="n">
         <v>994</v>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>248</v>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>708</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1143,10 +1447,16 @@
         </is>
       </c>
       <c r="B51" t="n">
+        <v>212</v>
+      </c>
+      <c r="C51" t="n">
         <v>676</v>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="n">
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>806</v>
+      </c>
+      <c r="F51" t="n">
         <v>248</v>
       </c>
     </row>
@@ -1157,12 +1467,18 @@
         </is>
       </c>
       <c r="B52" t="n">
+        <v>398</v>
+      </c>
+      <c r="C52" t="n">
         <v>1182</v>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>232</v>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>828</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1171,10 +1487,16 @@
         </is>
       </c>
       <c r="B53" t="n">
+        <v>451</v>
+      </c>
+      <c r="C53" t="n">
         <v>1030</v>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="n">
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>812</v>
+      </c>
+      <c r="F53" t="n">
         <v>222</v>
       </c>
     </row>
@@ -1185,12 +1507,18 @@
         </is>
       </c>
       <c r="B54" t="n">
+        <v>401</v>
+      </c>
+      <c r="C54" t="n">
         <v>1031</v>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>232</v>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>862</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1199,10 +1527,16 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>434</v>
+      </c>
+      <c r="C55" t="n">
         <v>1088</v>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="n">
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>840</v>
+      </c>
+      <c r="F55" t="n">
         <v>242</v>
       </c>
     </row>
@@ -1213,12 +1547,18 @@
         </is>
       </c>
       <c r="B56" t="n">
+        <v>446</v>
+      </c>
+      <c r="C56" t="n">
         <v>884</v>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>288</v>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>744</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1227,10 +1567,16 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>290</v>
+      </c>
+      <c r="C57" t="n">
         <v>990</v>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="n">
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>788</v>
+      </c>
+      <c r="F57" t="n">
         <v>212</v>
       </c>
     </row>
@@ -1241,12 +1587,18 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>375</v>
+      </c>
+      <c r="C58" t="n">
         <v>914</v>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>257</v>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>689</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -1255,12 +1607,18 @@
         </is>
       </c>
       <c r="B59" t="n">
+        <v>302</v>
+      </c>
+      <c r="C59" t="n">
         <v>822</v>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>276</v>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>702</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1269,10 +1627,16 @@
         </is>
       </c>
       <c r="B60" t="n">
+        <v>351</v>
+      </c>
+      <c r="C60" t="n">
         <v>970</v>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="n">
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>754</v>
+      </c>
+      <c r="F60" t="n">
         <v>160</v>
       </c>
     </row>
@@ -1283,12 +1647,18 @@
         </is>
       </c>
       <c r="B61" t="n">
+        <v>315</v>
+      </c>
+      <c r="C61" t="n">
         <v>850</v>
       </c>
-      <c r="C61" t="n">
+      <c r="D61" t="n">
         <v>242</v>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>672</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1297,10 +1667,16 @@
         </is>
       </c>
       <c r="B62" t="n">
+        <v>285</v>
+      </c>
+      <c r="C62" t="n">
         <v>972</v>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="n">
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>952</v>
+      </c>
+      <c r="F62" t="n">
         <v>210</v>
       </c>
     </row>
@@ -1311,12 +1687,18 @@
         </is>
       </c>
       <c r="B63" t="n">
+        <v>498</v>
+      </c>
+      <c r="C63" t="n">
         <v>982</v>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>216</v>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>830</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1325,10 +1707,16 @@
         </is>
       </c>
       <c r="B64" t="n">
+        <v>296</v>
+      </c>
+      <c r="C64" t="n">
         <v>1048</v>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="n">
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>758</v>
+      </c>
+      <c r="F64" t="n">
         <v>208</v>
       </c>
     </row>
@@ -1339,12 +1727,18 @@
         </is>
       </c>
       <c r="B65" t="n">
+        <v>536</v>
+      </c>
+      <c r="C65" t="n">
         <v>982</v>
       </c>
-      <c r="C65" t="n">
+      <c r="D65" t="n">
         <v>292</v>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>830</v>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1353,10 +1747,16 @@
         </is>
       </c>
       <c r="B66" t="n">
+        <v>348</v>
+      </c>
+      <c r="C66" t="n">
         <v>938</v>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="n">
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>740</v>
+      </c>
+      <c r="F66" t="n">
         <v>214</v>
       </c>
     </row>
@@ -1367,12 +1767,18 @@
         </is>
       </c>
       <c r="B67" t="n">
+        <v>68</v>
+      </c>
+      <c r="C67" t="n">
         <v>1100</v>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>230</v>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>814</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1381,10 +1787,16 @@
         </is>
       </c>
       <c r="B68" t="n">
+        <v>318</v>
+      </c>
+      <c r="C68" t="n">
         <v>928</v>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="n">
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>708</v>
+      </c>
+      <c r="F68" t="n">
         <v>206</v>
       </c>
     </row>
@@ -1395,10 +1807,16 @@
         </is>
       </c>
       <c r="B69" t="n">
+        <v>500</v>
+      </c>
+      <c r="C69" t="n">
         <v>1080</v>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="n">
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>508</v>
+      </c>
+      <c r="F69" t="n">
         <v>224</v>
       </c>
     </row>
@@ -1409,12 +1827,18 @@
         </is>
       </c>
       <c r="B70" t="n">
+        <v>356</v>
+      </c>
+      <c r="C70" t="n">
         <v>1046</v>
       </c>
-      <c r="C70" t="n">
+      <c r="D70" t="n">
         <v>312</v>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>734</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1423,10 +1847,16 @@
         </is>
       </c>
       <c r="B71" t="n">
+        <v>728</v>
+      </c>
+      <c r="C71" t="n">
         <v>1024</v>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="n">
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>882</v>
+      </c>
+      <c r="F71" t="n">
         <v>214</v>
       </c>
     </row>
@@ -1437,12 +1867,18 @@
         </is>
       </c>
       <c r="B72" t="n">
+        <v>347</v>
+      </c>
+      <c r="C72" t="n">
         <v>1170</v>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>230</v>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>740</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1451,10 +1887,16 @@
         </is>
       </c>
       <c r="B73" t="n">
+        <v>376</v>
+      </c>
+      <c r="C73" t="n">
         <v>1138</v>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="n">
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>750</v>
+      </c>
+      <c r="F73" t="n">
         <v>212</v>
       </c>
     </row>
@@ -1465,12 +1907,18 @@
         </is>
       </c>
       <c r="B74" t="n">
+        <v>482</v>
+      </c>
+      <c r="C74" t="n">
         <v>1278</v>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>230</v>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>826</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1479,10 +1927,16 @@
         </is>
       </c>
       <c r="B75" t="n">
+        <v>270</v>
+      </c>
+      <c r="C75" t="n">
         <v>1104</v>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>806</v>
+      </c>
+      <c r="F75" t="n">
         <v>232</v>
       </c>
     </row>
@@ -1493,12 +1947,18 @@
         </is>
       </c>
       <c r="B76" t="n">
+        <v>400</v>
+      </c>
+      <c r="C76" t="n">
         <v>1090</v>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>236</v>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>774</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -1507,10 +1967,16 @@
         </is>
       </c>
       <c r="B77" t="n">
+        <v>541</v>
+      </c>
+      <c r="C77" t="n">
         <v>1186</v>
       </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="n">
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>800</v>
+      </c>
+      <c r="F77" t="n">
         <v>212</v>
       </c>
     </row>
@@ -1521,12 +1987,18 @@
         </is>
       </c>
       <c r="B78" t="n">
+        <v>416</v>
+      </c>
+      <c r="C78" t="n">
         <v>1176</v>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>254</v>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>814</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1535,10 +2007,16 @@
         </is>
       </c>
       <c r="B79" t="n">
+        <v>334</v>
+      </c>
+      <c r="C79" t="n">
         <v>1022</v>
       </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="n">
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>802</v>
+      </c>
+      <c r="F79" t="n">
         <v>214</v>
       </c>
     </row>
@@ -1549,12 +2027,18 @@
         </is>
       </c>
       <c r="B80" t="n">
+        <v>770</v>
+      </c>
+      <c r="C80" t="n">
         <v>1144</v>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>244</v>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="n">
+        <v>732</v>
+      </c>
+      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -1563,10 +2047,16 @@
         </is>
       </c>
       <c r="B81" t="n">
+        <v>413</v>
+      </c>
+      <c r="C81" t="n">
         <v>1136</v>
       </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="n">
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="n">
+        <v>727</v>
+      </c>
+      <c r="F81" t="n">
         <v>276</v>
       </c>
     </row>
@@ -1577,12 +2067,18 @@
         </is>
       </c>
       <c r="B82" t="n">
+        <v>290</v>
+      </c>
+      <c r="C82" t="n">
         <v>1110</v>
       </c>
-      <c r="C82" t="n">
+      <c r="D82" t="n">
         <v>228</v>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="n">
+        <v>762</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1591,10 +2087,16 @@
         </is>
       </c>
       <c r="B83" t="n">
+        <v>336</v>
+      </c>
+      <c r="C83" t="n">
         <v>1370</v>
       </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="n">
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>902</v>
+      </c>
+      <c r="F83" t="n">
         <v>214</v>
       </c>
     </row>
@@ -1605,12 +2107,18 @@
         </is>
       </c>
       <c r="B84" t="n">
+        <v>344</v>
+      </c>
+      <c r="C84" t="n">
         <v>1050</v>
       </c>
-      <c r="C84" t="n">
+      <c r="D84" t="n">
         <v>270</v>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>768</v>
+      </c>
+      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -1619,10 +2127,16 @@
         </is>
       </c>
       <c r="B85" t="n">
+        <v>295</v>
+      </c>
+      <c r="C85" t="n">
         <v>1100</v>
       </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="n">
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="n">
+        <v>782</v>
+      </c>
+      <c r="F85" t="n">
         <v>214</v>
       </c>
     </row>
@@ -1633,12 +2147,18 @@
         </is>
       </c>
       <c r="B86" t="n">
+        <v>333</v>
+      </c>
+      <c r="C86" t="n">
         <v>1000</v>
       </c>
-      <c r="C86" t="n">
+      <c r="D86" t="n">
         <v>234</v>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="n">
+        <v>696</v>
+      </c>
+      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -1647,10 +2167,16 @@
         </is>
       </c>
       <c r="B87" t="n">
+        <v>322</v>
+      </c>
+      <c r="C87" t="n">
         <v>1078</v>
       </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="n">
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>854</v>
+      </c>
+      <c r="F87" t="n">
         <v>212</v>
       </c>
     </row>
@@ -1661,12 +2187,18 @@
         </is>
       </c>
       <c r="B88" t="n">
+        <v>388</v>
+      </c>
+      <c r="C88" t="n">
         <v>1392</v>
       </c>
-      <c r="C88" t="n">
+      <c r="D88" t="n">
         <v>264</v>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="n">
+        <v>816</v>
+      </c>
+      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -1675,10 +2207,16 @@
         </is>
       </c>
       <c r="B89" t="n">
+        <v>332</v>
+      </c>
+      <c r="C89" t="n">
         <v>1266</v>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="n">
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="n">
+        <v>798</v>
+      </c>
+      <c r="F89" t="n">
         <v>214</v>
       </c>
     </row>
@@ -1689,12 +2227,18 @@
         </is>
       </c>
       <c r="B90" t="n">
+        <v>347</v>
+      </c>
+      <c r="C90" t="n">
         <v>1004</v>
       </c>
-      <c r="C90" t="n">
+      <c r="D90" t="n">
         <v>288</v>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>715</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -1703,10 +2247,16 @@
         </is>
       </c>
       <c r="B91" t="n">
+        <v>418</v>
+      </c>
+      <c r="C91" t="n">
         <v>1156</v>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="n">
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="n">
+        <v>758</v>
+      </c>
+      <c r="F91" t="n">
         <v>220</v>
       </c>
     </row>
@@ -1717,12 +2267,18 @@
         </is>
       </c>
       <c r="B92" t="n">
+        <v>428</v>
+      </c>
+      <c r="C92" t="n">
         <v>1280</v>
       </c>
-      <c r="C92" t="n">
+      <c r="D92" t="n">
         <v>216</v>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>794</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -1731,10 +2287,16 @@
         </is>
       </c>
       <c r="B93" t="n">
+        <v>334</v>
+      </c>
+      <c r="C93" t="n">
         <v>1212</v>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="n">
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="n">
+        <v>848</v>
+      </c>
+      <c r="F93" t="n">
         <v>234</v>
       </c>
     </row>
@@ -1745,10 +2307,16 @@
         </is>
       </c>
       <c r="B94" t="n">
+        <v>315</v>
+      </c>
+      <c r="C94" t="n">
         <v>1319</v>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="n">
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="n">
+        <v>744</v>
+      </c>
+      <c r="F94" t="n">
         <v>220</v>
       </c>
     </row>
@@ -1759,12 +2327,18 @@
         </is>
       </c>
       <c r="B95" t="n">
+        <v>470</v>
+      </c>
+      <c r="C95" t="n">
         <v>1057</v>
       </c>
-      <c r="C95" t="n">
+      <c r="D95" t="n">
         <v>229</v>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>804</v>
+      </c>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -1773,10 +2347,16 @@
         </is>
       </c>
       <c r="B96" t="n">
+        <v>376</v>
+      </c>
+      <c r="C96" t="n">
         <v>1280</v>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="n">
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>796</v>
+      </c>
+      <c r="F96" t="n">
         <v>216</v>
       </c>
     </row>
@@ -1787,12 +2367,18 @@
         </is>
       </c>
       <c r="B97" t="n">
+        <v>451</v>
+      </c>
+      <c r="C97" t="n">
         <v>1145</v>
       </c>
-      <c r="C97" t="n">
+      <c r="D97" t="n">
         <v>234</v>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="n">
+        <v>763</v>
+      </c>
+      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -1801,12 +2387,18 @@
         </is>
       </c>
       <c r="B98" t="n">
+        <v>435</v>
+      </c>
+      <c r="C98" t="n">
         <v>1360</v>
       </c>
-      <c r="C98" t="n">
+      <c r="D98" t="n">
         <v>250</v>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="n">
+        <v>883</v>
+      </c>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -1815,10 +2407,16 @@
         </is>
       </c>
       <c r="B99" t="n">
+        <v>353</v>
+      </c>
+      <c r="C99" t="n">
         <v>1158</v>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="n">
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="n">
+        <v>772</v>
+      </c>
+      <c r="F99" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1829,12 +2427,18 @@
         </is>
       </c>
       <c r="B100" t="n">
+        <v>521</v>
+      </c>
+      <c r="C100" t="n">
         <v>1349</v>
       </c>
-      <c r="C100" t="n">
+      <c r="D100" t="n">
         <v>225</v>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="n">
+        <v>846</v>
+      </c>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -1843,10 +2447,16 @@
         </is>
       </c>
       <c r="B101" t="n">
+        <v>286</v>
+      </c>
+      <c r="C101" t="n">
         <v>1053</v>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="n">
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="n">
+        <v>722</v>
+      </c>
+      <c r="F101" t="n">
         <v>293</v>
       </c>
     </row>
@@ -1857,12 +2467,18 @@
         </is>
       </c>
       <c r="B102" t="n">
+        <v>376</v>
+      </c>
+      <c r="C102" t="n">
         <v>1332</v>
       </c>
-      <c r="C102" t="n">
+      <c r="D102" t="n">
         <v>275</v>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="n">
+        <v>915</v>
+      </c>
+      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -1871,10 +2487,16 @@
         </is>
       </c>
       <c r="B103" t="n">
+        <v>442</v>
+      </c>
+      <c r="C103" t="n">
         <v>1132</v>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="n">
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="n">
+        <v>758</v>
+      </c>
+      <c r="F103" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1885,12 +2507,18 @@
         </is>
       </c>
       <c r="B104" t="n">
+        <v>382</v>
+      </c>
+      <c r="C104" t="n">
         <v>1159</v>
       </c>
-      <c r="C104" t="n">
+      <c r="D104" t="n">
         <v>238</v>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="n">
+        <v>763</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -1899,12 +2527,18 @@
         </is>
       </c>
       <c r="B105" t="n">
+        <v>415</v>
+      </c>
+      <c r="C105" t="n">
         <v>1251</v>
       </c>
-      <c r="C105" t="n">
+      <c r="D105" t="n">
         <v>235</v>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="n">
+        <v>883</v>
+      </c>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -1913,10 +2547,16 @@
         </is>
       </c>
       <c r="B106" t="n">
+        <v>425</v>
+      </c>
+      <c r="C106" t="n">
         <v>1227</v>
       </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="n">
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="n">
+        <v>730</v>
+      </c>
+      <c r="F106" t="n">
         <v>211</v>
       </c>
     </row>
@@ -1927,10 +2567,16 @@
         </is>
       </c>
       <c r="B107" t="n">
+        <v>344</v>
+      </c>
+      <c r="C107" t="n">
         <v>1239</v>
       </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="n">
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="n">
+        <v>834</v>
+      </c>
+      <c r="F107" t="n">
         <v>215</v>
       </c>
     </row>
@@ -1941,12 +2587,18 @@
         </is>
       </c>
       <c r="B108" t="n">
+        <v>296</v>
+      </c>
+      <c r="C108" t="n">
         <v>960</v>
       </c>
-      <c r="C108" t="n">
+      <c r="D108" t="n">
         <v>256</v>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="n">
+        <v>738</v>
+      </c>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -1955,10 +2607,16 @@
         </is>
       </c>
       <c r="B109" t="n">
+        <v>584</v>
+      </c>
+      <c r="C109" t="n">
         <v>1141</v>
       </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="n">
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="n">
+        <v>735</v>
+      </c>
+      <c r="F109" t="n">
         <v>247</v>
       </c>
     </row>
@@ -1969,12 +2627,18 @@
         </is>
       </c>
       <c r="B110" t="n">
+        <v>331</v>
+      </c>
+      <c r="C110" t="n">
         <v>1173</v>
       </c>
-      <c r="C110" t="n">
+      <c r="D110" t="n">
         <v>224</v>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="n">
+        <v>777</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -1983,10 +2647,16 @@
         </is>
       </c>
       <c r="B111" t="n">
+        <v>347</v>
+      </c>
+      <c r="C111" t="n">
         <v>1162</v>
       </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="n">
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="n">
+        <v>774</v>
+      </c>
+      <c r="F111" t="n">
         <v>209</v>
       </c>
     </row>
@@ -1997,12 +2667,18 @@
         </is>
       </c>
       <c r="B112" t="n">
+        <v>596</v>
+      </c>
+      <c r="C112" t="n">
         <v>1121</v>
       </c>
-      <c r="C112" t="n">
+      <c r="D112" t="n">
         <v>237</v>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="n">
+        <v>821</v>
+      </c>
+      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -2011,10 +2687,16 @@
         </is>
       </c>
       <c r="B113" t="n">
+        <v>212</v>
+      </c>
+      <c r="C113" t="n">
         <v>1128</v>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="n">
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="n">
+        <v>755</v>
+      </c>
+      <c r="F113" t="n">
         <v>207</v>
       </c>
     </row>
@@ -2025,12 +2707,18 @@
         </is>
       </c>
       <c r="B114" t="n">
+        <v>474</v>
+      </c>
+      <c r="C114" t="n">
         <v>1428</v>
       </c>
-      <c r="C114" t="n">
+      <c r="D114" t="n">
         <v>236</v>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="n">
+        <v>1019</v>
+      </c>
+      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -2039,10 +2727,16 @@
         </is>
       </c>
       <c r="B115" t="n">
+        <v>491</v>
+      </c>
+      <c r="C115" t="n">
         <v>1231</v>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="n">
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="n">
+        <v>809</v>
+      </c>
+      <c r="F115" t="n">
         <v>205</v>
       </c>
     </row>
@@ -2053,12 +2747,18 @@
         </is>
       </c>
       <c r="B116" t="n">
+        <v>322</v>
+      </c>
+      <c r="C116" t="n">
         <v>1247</v>
       </c>
-      <c r="C116" t="n">
+      <c r="D116" t="n">
         <v>223</v>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="n">
+        <v>780</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -2067,10 +2767,16 @@
         </is>
       </c>
       <c r="B117" t="n">
+        <v>412</v>
+      </c>
+      <c r="C117" t="n">
         <v>1253</v>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="n">
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F117" t="n">
         <v>215</v>
       </c>
     </row>
@@ -2081,12 +2787,18 @@
         </is>
       </c>
       <c r="B118" t="n">
+        <v>314</v>
+      </c>
+      <c r="C118" t="n">
         <v>1006</v>
       </c>
-      <c r="C118" t="n">
+      <c r="D118" t="n">
         <v>339</v>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="n">
+        <v>703</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -2095,10 +2807,16 @@
         </is>
       </c>
       <c r="B119" t="n">
+        <v>340</v>
+      </c>
+      <c r="C119" t="n">
         <v>1077</v>
       </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="n">
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="n">
+        <v>767</v>
+      </c>
+      <c r="F119" t="n">
         <v>222</v>
       </c>
     </row>
@@ -2109,12 +2827,18 @@
         </is>
       </c>
       <c r="B120" t="n">
+        <v>382</v>
+      </c>
+      <c r="C120" t="n">
         <v>1221</v>
       </c>
-      <c r="C120" t="n">
+      <c r="D120" t="n">
         <v>233</v>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="n">
+        <v>806</v>
+      </c>
+      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -2123,10 +2847,16 @@
         </is>
       </c>
       <c r="B121" t="n">
+        <v>330</v>
+      </c>
+      <c r="C121" t="n">
         <v>1005</v>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="n">
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="n">
+        <v>810</v>
+      </c>
+      <c r="F121" t="n">
         <v>249</v>
       </c>
     </row>
@@ -2137,12 +2867,18 @@
         </is>
       </c>
       <c r="B122" t="n">
+        <v>334</v>
+      </c>
+      <c r="C122" t="n">
         <v>1084</v>
       </c>
-      <c r="C122" t="n">
+      <c r="D122" t="n">
         <v>303</v>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="n">
+        <v>735</v>
+      </c>
+      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -2151,10 +2887,16 @@
         </is>
       </c>
       <c r="B123" t="n">
+        <v>674</v>
+      </c>
+      <c r="C123" t="n">
         <v>1469</v>
       </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="n">
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="n">
+        <v>859</v>
+      </c>
+      <c r="F123" t="n">
         <v>214</v>
       </c>
     </row>
@@ -2165,12 +2907,18 @@
         </is>
       </c>
       <c r="B124" t="n">
+        <v>443</v>
+      </c>
+      <c r="C124" t="n">
         <v>1067</v>
       </c>
-      <c r="C124" t="n">
+      <c r="D124" t="n">
         <v>367</v>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="n">
+        <v>743</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -2179,10 +2927,16 @@
         </is>
       </c>
       <c r="B125" t="n">
+        <v>387</v>
+      </c>
+      <c r="C125" t="n">
         <v>1076</v>
       </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="n">
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="n">
+        <v>688</v>
+      </c>
+      <c r="F125" t="n">
         <v>271</v>
       </c>
     </row>
@@ -2193,12 +2947,18 @@
         </is>
       </c>
       <c r="B126" t="n">
+        <v>439</v>
+      </c>
+      <c r="C126" t="n">
         <v>1124</v>
       </c>
-      <c r="C126" t="n">
+      <c r="D126" t="n">
         <v>275</v>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="n">
+        <v>880</v>
+      </c>
+      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -2207,12 +2967,18 @@
         </is>
       </c>
       <c r="B127" t="n">
+        <v>371</v>
+      </c>
+      <c r="C127" t="n">
         <v>1105</v>
       </c>
-      <c r="C127" t="n">
+      <c r="D127" t="n">
         <v>347</v>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="n">
+        <v>859</v>
+      </c>
+      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -2221,12 +2987,18 @@
         </is>
       </c>
       <c r="B128" t="n">
+        <v>391</v>
+      </c>
+      <c r="C128" t="n">
         <v>984</v>
       </c>
-      <c r="C128" t="n">
+      <c r="D128" t="n">
         <v>334</v>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="n">
+        <v>685</v>
+      </c>
+      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -2235,12 +3007,18 @@
         </is>
       </c>
       <c r="B129" t="n">
+        <v>376</v>
+      </c>
+      <c r="C129" t="n">
         <v>1168</v>
       </c>
-      <c r="C129" t="n">
+      <c r="D129" t="n">
         <v>331</v>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="n">
+        <v>765</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -2249,10 +3027,16 @@
         </is>
       </c>
       <c r="B130" t="n">
+        <v>374</v>
+      </c>
+      <c r="C130" t="n">
         <v>1202</v>
       </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="n">
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="n">
+        <v>834</v>
+      </c>
+      <c r="F130" t="n">
         <v>214</v>
       </c>
     </row>
@@ -2263,12 +3047,18 @@
         </is>
       </c>
       <c r="B131" t="n">
+        <v>351</v>
+      </c>
+      <c r="C131" t="n">
         <v>1011</v>
       </c>
-      <c r="C131" t="n">
+      <c r="D131" t="n">
         <v>298</v>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="n">
+        <v>749</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -2277,10 +3067,16 @@
         </is>
       </c>
       <c r="B132" t="n">
+        <v>23</v>
+      </c>
+      <c r="C132" t="n">
         <v>1164</v>
       </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="n">
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="n">
+        <v>14</v>
+      </c>
+      <c r="F132" t="n">
         <v>234</v>
       </c>
     </row>
@@ -2291,12 +3087,18 @@
         </is>
       </c>
       <c r="B133" t="n">
+        <v>389</v>
+      </c>
+      <c r="C133" t="n">
         <v>1207</v>
       </c>
-      <c r="C133" t="n">
+      <c r="D133" t="n">
         <v>145</v>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="n">
+        <v>819</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -2305,10 +3107,16 @@
         </is>
       </c>
       <c r="B134" t="n">
+        <v>183</v>
+      </c>
+      <c r="C134" t="n">
         <v>1202</v>
       </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="n">
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="n">
+        <v>857</v>
+      </c>
+      <c r="F134" t="n">
         <v>216</v>
       </c>
     </row>
@@ -2319,12 +3127,18 @@
         </is>
       </c>
       <c r="B135" t="n">
+        <v>499</v>
+      </c>
+      <c r="C135" t="n">
         <v>938</v>
       </c>
-      <c r="C135" t="n">
+      <c r="D135" t="n">
         <v>328</v>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="n">
+        <v>689</v>
+      </c>
+      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -2333,10 +3147,16 @@
         </is>
       </c>
       <c r="B136" t="n">
+        <v>507</v>
+      </c>
+      <c r="C136" t="n">
         <v>1013</v>
       </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="n">
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="n">
+        <v>856</v>
+      </c>
+      <c r="F136" t="n">
         <v>142</v>
       </c>
     </row>
@@ -2347,12 +3167,18 @@
         </is>
       </c>
       <c r="B137" t="n">
+        <v>464</v>
+      </c>
+      <c r="C137" t="n">
         <v>1347</v>
       </c>
-      <c r="C137" t="n">
+      <c r="D137" t="n">
         <v>301</v>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="n">
+        <v>964</v>
+      </c>
+      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -2361,10 +3187,16 @@
         </is>
       </c>
       <c r="B138" t="n">
+        <v>338</v>
+      </c>
+      <c r="C138" t="n">
         <v>1118</v>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="n">
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="n">
+        <v>816</v>
+      </c>
+      <c r="F138" t="n">
         <v>210</v>
       </c>
     </row>
@@ -2375,12 +3207,18 @@
         </is>
       </c>
       <c r="B139" t="n">
+        <v>527</v>
+      </c>
+      <c r="C139" t="n">
         <v>1244</v>
       </c>
-      <c r="C139" t="n">
+      <c r="D139" t="n">
         <v>454</v>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="n">
+        <v>849</v>
+      </c>
+      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -2389,12 +3227,18 @@
         </is>
       </c>
       <c r="B140" t="n">
+        <v>435</v>
+      </c>
+      <c r="C140" t="n">
         <v>1090</v>
       </c>
-      <c r="C140" t="n">
+      <c r="D140" t="n">
         <v>306</v>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="n">
+        <v>767</v>
+      </c>
+      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -2403,10 +3247,16 @@
         </is>
       </c>
       <c r="B141" t="n">
+        <v>426</v>
+      </c>
+      <c r="C141" t="n">
         <v>1007</v>
       </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="n">
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="n">
+        <v>718</v>
+      </c>
+      <c r="F141" t="n">
         <v>207</v>
       </c>
     </row>
